--- a/test.xlsx
+++ b/test.xlsx
@@ -1,26 +1,140 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23bur\Projects\School\CPS210\Programs\P2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704AF88D-69F4-4B11-BDDC-FF97CC1A7D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="maze" sheetId="1" r:id="rId1"/>
+    <sheet name="maze 2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Benjamin King</author>
+  </authors>
+  <commentList>
+    <comment ref="AE6" authorId="0" shapeId="0" xr:uid="{20452623-044F-438F-BA1E-37C8A5DF6990}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Benjamin King:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+min(m x n) - 1</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Node</t>
+  </si>
+  <si>
+    <t>is_start</t>
+  </si>
+  <si>
+    <t>is_end</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>(right value)</t>
+  </si>
+  <si>
+    <t>queue:</t>
+  </si>
+  <si>
+    <t>prev_val:</t>
+  </si>
+  <si>
+    <t>current:</t>
+  </si>
+  <si>
+    <t>val_after</t>
+  </si>
+  <si>
+    <t>has_moved</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>prev_val</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>queue</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>set_queue_max</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +142,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -45,14 +184,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +587,1014 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="10" width="7.140625" customWidth="1"/>
+    <col min="13" max="22" width="7.85546875" customWidth="1"/>
+    <col min="28" max="28" width="10.85546875" customWidth="1"/>
+    <col min="29" max="29" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3">
+        <v>1</v>
+      </c>
+      <c r="M1" s="1">
+        <v>-1</v>
+      </c>
+      <c r="N1" s="10">
+        <v>0</v>
+      </c>
+      <c r="O1" s="2">
+        <v>-1</v>
+      </c>
+      <c r="P1" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q1" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R1" s="2">
+        <v>-1</v>
+      </c>
+      <c r="S1" s="2">
+        <v>-1</v>
+      </c>
+      <c r="T1" s="2">
+        <v>-1</v>
+      </c>
+      <c r="U1" s="2">
+        <v>-1</v>
+      </c>
+      <c r="V1" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>1</v>
+      </c>
+      <c r="J2" s="6">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4">
+        <v>-1</v>
+      </c>
+      <c r="N2" s="12">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5">
+        <v>-1</v>
+      </c>
+      <c r="P2" s="12">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="12">
+        <v>8</v>
+      </c>
+      <c r="R2" s="12">
+        <v>9</v>
+      </c>
+      <c r="S2" s="12">
+        <v>10</v>
+      </c>
+      <c r="T2" s="12">
+        <v>11</v>
+      </c>
+      <c r="U2" s="12">
+        <v>12</v>
+      </c>
+      <c r="V2" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4">
+        <v>-1</v>
+      </c>
+      <c r="N3" s="12">
+        <v>2</v>
+      </c>
+      <c r="O3" s="5">
+        <v>-1</v>
+      </c>
+      <c r="P3" s="12">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>-1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>-1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>-1</v>
+      </c>
+      <c r="T3" s="5">
+        <v>-1</v>
+      </c>
+      <c r="U3" s="12">
+        <v>13</v>
+      </c>
+      <c r="V3" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
+        <v>-1</v>
+      </c>
+      <c r="N4" s="12">
+        <v>3</v>
+      </c>
+      <c r="O4" s="12">
+        <v>4</v>
+      </c>
+      <c r="P4" s="12">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>6</v>
+      </c>
+      <c r="R4" s="12">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>-1</v>
+      </c>
+      <c r="T4" s="5">
+        <v>-1</v>
+      </c>
+      <c r="U4" s="12">
+        <v>14</v>
+      </c>
+      <c r="V4" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>-1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="O5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="P5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="R5" s="12">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="T5" s="12">
+        <v>16</v>
+      </c>
+      <c r="U5" s="12">
+        <v>15</v>
+      </c>
+      <c r="V5" s="12">
+        <v>16</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4">
+        <v>-1</v>
+      </c>
+      <c r="N6" s="12">
+        <v>13</v>
+      </c>
+      <c r="O6" s="12">
+        <v>12</v>
+      </c>
+      <c r="P6" s="12">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>10</v>
+      </c>
+      <c r="R6" s="12">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>-1</v>
+      </c>
+      <c r="T6" s="5">
+        <v>-1</v>
+      </c>
+      <c r="U6" s="12">
+        <v>16</v>
+      </c>
+      <c r="V6" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Y6" s="12"/>
+      <c r="AE6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4">
+        <v>-1</v>
+      </c>
+      <c r="N7" s="12">
+        <v>14</v>
+      </c>
+      <c r="O7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="P7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="R7" s="12">
+        <v>10</v>
+      </c>
+      <c r="S7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="T7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="U7" s="12">
+        <v>15</v>
+      </c>
+      <c r="V7" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="6">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4">
+        <v>-1</v>
+      </c>
+      <c r="N8" s="12">
+        <v>15</v>
+      </c>
+      <c r="O8" s="12">
+        <v>14</v>
+      </c>
+      <c r="P8" s="12">
+        <v>13</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>12</v>
+      </c>
+      <c r="R8" s="12">
+        <v>11</v>
+      </c>
+      <c r="S8" s="12">
+        <v>12</v>
+      </c>
+      <c r="T8" s="12">
+        <v>13</v>
+      </c>
+      <c r="U8" s="12">
+        <v>14</v>
+      </c>
+      <c r="V8" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="9">
+        <v>1</v>
+      </c>
+      <c r="M9" s="7">
+        <v>-1</v>
+      </c>
+      <c r="N9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="O9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="P9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="S9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="T9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="U9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="V9" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W10" t="s">
+        <v>8</v>
+      </c>
+      <c r="X10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1:V1 M1 Y6 M2:V9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F28EFAE-B05E-4F20-91E0-B527435335A5}">
+  <dimension ref="A4:Q16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <f>SQRT(10*10+9*9)</f>
+        <v>13.45362404707371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="L5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="O5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="P5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <v>3</v>
+      </c>
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>5</v>
+      </c>
+      <c r="N6" s="5">
+        <v>6</v>
+      </c>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>4</v>
+      </c>
+      <c r="L7" s="5">
+        <v>5</v>
+      </c>
+      <c r="M7" s="5">
+        <v>6</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5">
+        <v>4</v>
+      </c>
+      <c r="K8" s="5">
+        <v>5</v>
+      </c>
+      <c r="L8" s="5">
+        <v>6</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>4</v>
+      </c>
+      <c r="J9" s="5">
+        <v>5</v>
+      </c>
+      <c r="K9" s="5">
+        <v>6</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H10" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>5</v>
+      </c>
+      <c r="J10" s="5">
+        <v>6</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="5">
+        <v>6</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H13" s="7">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="L13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="M13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="O13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="P13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="J5:Q5 H5 H6:Q8 H9:P9 H10:Q13 I16:L16 I6:P12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>